--- a/DXLibProject_Start/Data/CSV/DragonModel.xlsx
+++ b/DXLibProject_Start/Data/CSV/DragonModel.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,16 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\2nd_3DAction\DXLibProject_Start\Data\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{74EDCD3C-698D-4462-9D07-ED04A979920B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EDCE4DF-7C43-4182-B741-A0C9D5456856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1755" yWindow="2760" windowWidth="21600" windowHeight="11295"/>
+    <workbookView xWindow="-225" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DragonModelPath" sheetId="1" r:id="rId1"/>
     <sheet name="Status" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -53,9 +62,6 @@
   </si>
   <si>
     <t>animPath[4]</t>
-  </si>
-  <si>
-    <t>Resource\\Player\\ChaWitch\\</t>
   </si>
   <si>
     <t>Motions\\</t>
@@ -110,12 +116,15 @@
     <t>Attack.mv1</t>
     <phoneticPr fontId="20"/>
   </si>
+  <si>
+    <t>Resource\\Dragon\\ChaDragon\\</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="21" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -288,6 +297,12 @@
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Yu Gothic UI"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="33">
@@ -715,11 +730,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1076,7 +1094,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1110,49 +1128,50 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
       </c>
       <c r="D2">
         <f>Status!B6</f>
         <v>5</v>
       </c>
       <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" t="s">
         <v>12</v>
       </c>
-      <c r="F2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>13</v>
-      </c>
-      <c r="I2" t="s">
-        <v>14</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="20"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B1">
         <v>0</v>
@@ -1160,7 +1179,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -1168,7 +1187,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -1176,7 +1195,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -1184,7 +1203,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -1192,7 +1211,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6">
         <v>5</v>

--- a/DXLibProject_Start/Data/CSV/DragonModel.xlsx
+++ b/DXLibProject_Start/Data/CSV/DragonModel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\2nd_3DAction\DXLibProject_Start\Data\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EDCE4DF-7C43-4182-B741-A0C9D5456856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C003EEB6-A97A-4A74-B625-E543AA4776BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-225" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6555" yWindow="3255" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DragonModelPath" sheetId="1" r:id="rId1"/>
@@ -1097,6 +1097,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="5" max="7" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
